--- a/Pruebas calificadas/COLEGIO DE LA BICI (IED)-1102_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO DE LA BICI (IED)-1102_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -4361,7 +4301,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -4614,7 +4550,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -4867,7 +4799,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5108,11 +5040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -5120,7 +5048,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5361,11 +5289,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -5373,7 +5297,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5614,11 +5538,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -5626,7 +5546,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5867,11 +5787,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -5879,7 +5795,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6120,11 +6036,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800643</t>
@@ -6132,7 +6044,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA BICI (IED)</t>
+          <t>COLEGIO DE LA BICI</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
